--- a/public/office/excel/EmployeeAppraisalExcelTemplate/端午發放獎金調查範本.xlsx
+++ b/public/office/excel/EmployeeAppraisalExcelTemplate/端午發放獎金調查範本.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\apprasial\2026_06_03_apprasial_server-main\public\office\excel\EmployeeAppraisalExcelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\考核2026\2026_0608_apprasial_server\public\office\excel\EmployeeAppraisalExcelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5764ABE-A263-4AAC-9B58-C92EFB828FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="紀錄表" sheetId="4" r:id="rId1"/>
@@ -517,19 +517,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8DDC82-6BAE-44AD-BE3A-01A414F1A826}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.09765625" customWidth="1"/>
-    <col min="2" max="2" width="6.09765625" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="7.09765625" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="9" width="11.09765625" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" customWidth="1"/>
-    <col min="12" max="12" width="12.19921875" customWidth="1"/>
+    <col min="6" max="9" width="11.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="31.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -543,7 +543,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" ht="22.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="22.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -555,7 +555,7 @@
       <c r="I2" s="4"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="22.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="22.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -573,7 +573,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
